--- a/1. Manutenção Turno A - Previsão de Gastos 2025 e 2026.xlsx
+++ b/1. Manutenção Turno A - Previsão de Gastos 2025 e 2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zeluzjunior\PycharmProjects\teste_visual\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\pcmauro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FBB26EA-5B68-4506-B7E3-6402FA4F6897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FFFC7D2-16E2-4B03-8BE8-8D939508E76B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="2" xr2:uid="{093689EF-D701-4890-B8A9-8BD8B50DC7E2}"/>
+    <workbookView xWindow="195" yWindow="480" windowWidth="28605" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{093689EF-D701-4890-B8A9-8BD8B50DC7E2}"/>
   </bookViews>
   <sheets>
     <sheet name="DADOS" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="958" uniqueCount="242">
   <si>
     <t>Status</t>
   </si>
@@ -217,6 +217,18 @@
   <si>
     <t>NÚMERO DA REQUISIÇÃO 
 DE COMPRA</t>
+  </si>
+  <si>
+    <t>NÚMERO DO 
+PEDIDO DE COMPRA</t>
+  </si>
+  <si>
+    <t>NF DE SERVIÇO
+ RECEBIDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NF ENVIADA
+ PARA LANÇAMENTO </t>
   </si>
   <si>
     <t>OBSERVAÇÕES</t>
@@ -796,10 +808,13 @@
     <t>SERVIÇO DE TERCEIRO COM MÃO DE OBRA E MATERIAL PARA USINAGEM DA BUCHA DO EIXO DA LÂMINA DA FATIADORA DE BISTECA V-CUT MAREL.</t>
   </si>
   <si>
-    <t>NÚMERO DO PEDIDO DE COMPRA</t>
+    <t>SERVIÇO PARA MÃO DE OBRA MAIS ITENS NECESSÁRIOS PARA CONSERTO EM IMPRESSORA MARKEM-IMAJE CN24300163</t>
   </si>
   <si>
-    <t>teste</t>
+    <t>TESTE</t>
+  </si>
+  <si>
+    <t>TESTE  2</t>
   </si>
 </sst>
 </file>
@@ -1006,7 +1021,7 @@
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1184,10 +1199,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -1378,7 +1389,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[1. Manutenção Turno A - Previsão de Gastos 2025 e 2026 (1).xlsx]DASHBOARD!Tabela dinâmica1</c:name>
+    <c:name>[1. Manutenção Turno A - Previsão de Gastos 2025 e 2026.xlsx]DASHBOARD!Tabela dinâmica1</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -15184,7 +15195,7 @@
     <col min="3" max="3" width="17.140625" style="21" customWidth="1"/>
     <col min="4" max="4" width="31.140625" style="22" customWidth="1"/>
     <col min="5" max="5" width="88.140625" style="26" customWidth="1"/>
-    <col min="6" max="6" width="19.5703125" style="23" customWidth="1"/>
+    <col min="6" max="6" width="14" style="23" customWidth="1"/>
     <col min="7" max="7" width="17.5703125" style="21" customWidth="1"/>
     <col min="8" max="8" width="10.7109375" style="21" customWidth="1"/>
     <col min="9" max="9" width="12.5703125" style="24" customWidth="1"/>
@@ -15245,19 +15256,19 @@
         <v>54</v>
       </c>
       <c r="O1" s="20" t="s">
-        <v>236</v>
+        <v>55</v>
       </c>
       <c r="P1" s="20" t="s">
         <v>4</v>
       </c>
       <c r="Q1" s="20" t="s">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="R1" s="20" t="s">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="S1" s="20" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -15268,13 +15279,13 @@
         <v>8</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F2" s="32">
         <v>885.1</v>
@@ -15289,7 +15300,7 @@
         <v>41758</v>
       </c>
       <c r="J2" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K2" s="36">
         <v>97223</v>
@@ -15298,7 +15309,7 @@
         <v>46010</v>
       </c>
       <c r="M2" s="28" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="N2" s="36">
         <v>4335900</v>
@@ -15316,7 +15327,7 @@
         <v>10</v>
       </c>
       <c r="S2" s="46" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -15327,13 +15338,13 @@
         <v>8</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F3" s="32">
         <v>6752</v>
@@ -15348,7 +15359,7 @@
         <v>40140</v>
       </c>
       <c r="J3" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K3" s="36">
         <v>95155</v>
@@ -15357,7 +15368,7 @@
         <v>46000</v>
       </c>
       <c r="M3" s="28" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="N3" s="36">
         <v>4325100</v>
@@ -15375,7 +15386,7 @@
         <v>10</v>
       </c>
       <c r="S3" s="46" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15386,13 +15397,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F4" s="32">
         <v>2109</v>
@@ -15407,7 +15418,7 @@
         <v>40688</v>
       </c>
       <c r="J4" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K4" s="36">
         <v>95152</v>
@@ -15416,7 +15427,7 @@
         <v>45995</v>
       </c>
       <c r="M4" s="28" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="N4" s="36">
         <v>4321296</v>
@@ -15434,7 +15445,7 @@
         <v>10</v>
       </c>
       <c r="S4" s="46" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -15445,13 +15456,13 @@
         <v>8</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F5" s="32">
         <v>1828</v>
@@ -15466,7 +15477,7 @@
         <v>40688</v>
       </c>
       <c r="J5" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K5" s="36">
         <v>95166</v>
@@ -15475,7 +15486,7 @@
         <v>45995</v>
       </c>
       <c r="M5" s="28" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="N5" s="36">
         <v>4321339</v>
@@ -15493,7 +15504,7 @@
         <v>10</v>
       </c>
       <c r="S5" s="46" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -15504,13 +15515,13 @@
         <v>8</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F6" s="32">
         <v>1710</v>
@@ -15525,7 +15536,7 @@
         <v>39324</v>
       </c>
       <c r="J6" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K6" s="36">
         <v>89444</v>
@@ -15534,7 +15545,7 @@
         <v>45961</v>
       </c>
       <c r="M6" s="28" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="N6" s="36">
         <v>4287592</v>
@@ -15552,7 +15563,7 @@
         <v>10</v>
       </c>
       <c r="S6" s="46" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -15563,13 +15574,13 @@
         <v>8</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F7" s="32">
         <v>16000</v>
@@ -15581,10 +15592,10 @@
         <v>242</v>
       </c>
       <c r="I7" s="34" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J7" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K7" s="36">
         <v>86110</v>
@@ -15593,7 +15604,7 @@
         <v>45943</v>
       </c>
       <c r="M7" s="28" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="N7" s="36">
         <v>4268451</v>
@@ -15611,7 +15622,7 @@
         <v>10</v>
       </c>
       <c r="S7" s="46" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -15622,13 +15633,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F8" s="32">
         <v>1102</v>
@@ -15643,7 +15654,7 @@
         <v>34945</v>
       </c>
       <c r="J8" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K8" s="36">
         <v>80971</v>
@@ -15652,7 +15663,7 @@
         <v>45924</v>
       </c>
       <c r="M8" s="28" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="N8" s="36">
         <v>4250909</v>
@@ -15670,7 +15681,7 @@
         <v>10</v>
       </c>
       <c r="S8" s="46" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -15681,13 +15692,13 @@
         <v>8</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F9" s="32">
         <v>4800</v>
@@ -15702,7 +15713,7 @@
         <v>41992</v>
       </c>
       <c r="J9" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K9" s="36">
         <v>101819</v>
@@ -15711,7 +15722,7 @@
         <v>46057</v>
       </c>
       <c r="M9" s="28" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="N9" s="36">
         <v>4381881</v>
@@ -15729,7 +15740,7 @@
         <v>10</v>
       </c>
       <c r="S9" s="46" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -15740,13 +15751,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F10" s="32">
         <v>1862.5</v>
@@ -15758,10 +15769,10 @@
         <v>242</v>
       </c>
       <c r="I10" s="52" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J10" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K10" s="36">
         <v>101851</v>
@@ -15770,7 +15781,7 @@
         <v>46056</v>
       </c>
       <c r="M10" s="28" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="N10" s="36">
         <v>4381124</v>
@@ -15788,7 +15799,7 @@
         <v>10</v>
       </c>
       <c r="S10" s="46" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -15799,13 +15810,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F11" s="32">
         <v>1745.8</v>
@@ -15820,7 +15831,7 @@
         <v>44138</v>
       </c>
       <c r="J11" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K11" s="36">
         <v>103379</v>
@@ -15829,7 +15840,7 @@
         <v>46055</v>
       </c>
       <c r="M11" s="28" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="N11" s="36">
         <v>4378656</v>
@@ -15847,7 +15858,7 @@
         <v>14</v>
       </c>
       <c r="S11" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -15858,13 +15869,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F12" s="32">
         <v>7710.6</v>
@@ -15879,7 +15890,7 @@
         <v>43646</v>
       </c>
       <c r="J12" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K12" s="36">
         <v>103385</v>
@@ -15888,7 +15899,7 @@
         <v>46055</v>
       </c>
       <c r="M12" s="28" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="N12" s="36">
         <v>4378710</v>
@@ -15906,7 +15917,7 @@
         <v>14</v>
       </c>
       <c r="S12" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -15917,13 +15928,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E13" s="31" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F13" s="32">
         <v>29405.919999999998</v>
@@ -15935,10 +15946,10 @@
         <v>242</v>
       </c>
       <c r="I13" s="34" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J13" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K13" s="36">
         <v>103172</v>
@@ -15947,7 +15958,7 @@
         <v>46050</v>
       </c>
       <c r="M13" s="28" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="N13" s="36">
         <v>4374285</v>
@@ -15965,7 +15976,7 @@
         <v>10</v>
       </c>
       <c r="S13" s="46" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -15976,13 +15987,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F14" s="32">
         <v>21721</v>
@@ -15994,10 +16005,10 @@
         <v>242</v>
       </c>
       <c r="I14" s="39" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J14" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K14" s="36">
         <v>103173</v>
@@ -16006,7 +16017,7 @@
         <v>46050</v>
       </c>
       <c r="M14" s="28" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="N14" s="36">
         <v>4374555</v>
@@ -16022,7 +16033,7 @@
         <v>14</v>
       </c>
       <c r="S14" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -16033,13 +16044,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D15" s="30" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E15" s="31" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F15" s="32">
         <v>19514.04</v>
@@ -16054,7 +16065,7 @@
         <v>44225</v>
       </c>
       <c r="J15" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K15" s="36">
         <v>101134</v>
@@ -16063,7 +16074,7 @@
         <v>46041</v>
       </c>
       <c r="M15" s="28" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="N15" s="36">
         <v>4363797</v>
@@ -16081,7 +16092,7 @@
         <v>10</v>
       </c>
       <c r="S15" s="46" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -16092,13 +16103,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D16" s="30" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F16" s="32">
         <v>7675.8</v>
@@ -16113,7 +16124,7 @@
         <v>41742</v>
       </c>
       <c r="J16" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K16" s="36">
         <v>100999</v>
@@ -16122,7 +16133,7 @@
         <v>46039</v>
       </c>
       <c r="M16" s="28" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="N16" s="36">
         <v>4362715</v>
@@ -16140,7 +16151,7 @@
         <v>14</v>
       </c>
       <c r="S16" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -16151,13 +16162,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E17" s="31" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F17" s="32">
         <v>7694.1</v>
@@ -16172,7 +16183,7 @@
         <v>42336</v>
       </c>
       <c r="J17" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K17" s="36">
         <v>101002</v>
@@ -16181,7 +16192,7 @@
         <v>46039</v>
       </c>
       <c r="M17" s="28" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="N17" s="36">
         <v>4362717</v>
@@ -16199,7 +16210,7 @@
         <v>14</v>
       </c>
       <c r="S17" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -16210,13 +16221,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F18" s="32">
         <v>16250</v>
@@ -16231,7 +16242,7 @@
         <v>42915</v>
       </c>
       <c r="J18" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K18" s="36">
         <v>99301</v>
@@ -16240,7 +16251,7 @@
         <v>46038</v>
       </c>
       <c r="M18" s="28" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="N18" s="36">
         <v>4361994</v>
@@ -16258,7 +16269,7 @@
         <v>10</v>
       </c>
       <c r="S18" s="46" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -16269,13 +16280,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D19" s="30" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E19" s="31" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F19" s="32">
         <v>38687.68</v>
@@ -16290,7 +16301,7 @@
         <v>43898</v>
       </c>
       <c r="J19" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K19" s="36">
         <v>100486</v>
@@ -16299,7 +16310,7 @@
         <v>46038</v>
       </c>
       <c r="M19" s="28" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="N19" s="36">
         <v>4362395</v>
@@ -16317,7 +16328,7 @@
         <v>10</v>
       </c>
       <c r="S19" s="46" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -16328,13 +16339,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D20" s="30" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E20" s="31" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F20" s="32">
         <v>759.9</v>
@@ -16349,7 +16360,7 @@
         <v>43689</v>
       </c>
       <c r="J20" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K20" s="36">
         <v>100103</v>
@@ -16358,7 +16369,7 @@
         <v>46036</v>
       </c>
       <c r="M20" s="28" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="N20" s="36">
         <v>4358863</v>
@@ -16376,7 +16387,7 @@
         <v>14</v>
       </c>
       <c r="S20" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -16387,13 +16398,13 @@
         <v>8</v>
       </c>
       <c r="C21" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D21" s="30" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E21" s="31" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F21" s="32">
         <v>1743.4</v>
@@ -16408,7 +16419,7 @@
         <v>43551</v>
       </c>
       <c r="J21" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K21" s="36">
         <v>100101</v>
@@ -16417,7 +16428,7 @@
         <v>46036</v>
       </c>
       <c r="M21" s="28" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="N21" s="36">
         <v>4358867</v>
@@ -16435,7 +16446,7 @@
         <v>10</v>
       </c>
       <c r="S21" s="46" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -16446,13 +16457,13 @@
         <v>8</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D22" s="30" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E22" s="31" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F22" s="32">
         <v>1239.9000000000001</v>
@@ -16467,7 +16478,7 @@
         <v>43551</v>
       </c>
       <c r="J22" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K22" s="36">
         <v>100118</v>
@@ -16476,7 +16487,7 @@
         <v>46036</v>
       </c>
       <c r="M22" s="28" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="N22" s="36">
         <v>4358873</v>
@@ -16494,7 +16505,7 @@
         <v>10</v>
       </c>
       <c r="S22" s="46" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="23" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -16505,13 +16516,13 @@
         <v>8</v>
       </c>
       <c r="C23" s="29" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D23" s="30" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E23" s="31" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F23" s="32">
         <v>4770</v>
@@ -16526,7 +16537,7 @@
         <v>40688</v>
       </c>
       <c r="J23" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K23" s="36">
         <v>100450</v>
@@ -16535,7 +16546,7 @@
         <v>46036</v>
       </c>
       <c r="M23" s="28" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="N23" s="36">
         <v>4358971</v>
@@ -16553,7 +16564,7 @@
         <v>14</v>
       </c>
       <c r="S23" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -16564,13 +16575,13 @@
         <v>8</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D24" s="30" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E24" s="31" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F24" s="32">
         <v>7159</v>
@@ -16585,7 +16596,7 @@
         <v>43688</v>
       </c>
       <c r="J24" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K24" s="36">
         <v>100122</v>
@@ -16594,7 +16605,7 @@
         <v>46036</v>
       </c>
       <c r="M24" s="28" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="N24" s="36">
         <v>4359129</v>
@@ -16612,7 +16623,7 @@
         <v>10</v>
       </c>
       <c r="S24" s="46" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -16623,13 +16634,13 @@
         <v>8</v>
       </c>
       <c r="C25" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D25" s="30" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E25" s="31" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F25" s="32">
         <v>98619.33</v>
@@ -16641,10 +16652,10 @@
         <v>242</v>
       </c>
       <c r="I25" s="34" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J25" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K25" s="36">
         <v>97334</v>
@@ -16653,7 +16664,7 @@
         <v>46036</v>
       </c>
       <c r="M25" s="28" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="N25" s="36">
         <v>4359165</v>
@@ -16671,7 +16682,7 @@
         <v>14</v>
       </c>
       <c r="S25" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -16682,13 +16693,13 @@
         <v>8</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D26" s="30" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E26" s="31" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F26" s="32">
         <v>1080</v>
@@ -16703,7 +16714,7 @@
         <v>43644</v>
       </c>
       <c r="J26" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K26" s="36">
         <v>100440</v>
@@ -16712,7 +16723,7 @@
         <v>46036</v>
       </c>
       <c r="M26" s="28" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="N26" s="36">
         <v>4359939</v>
@@ -16730,7 +16741,7 @@
         <v>14</v>
       </c>
       <c r="S26" s="49" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -16741,13 +16752,13 @@
         <v>8</v>
       </c>
       <c r="C27" s="29" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D27" s="30" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E27" s="31" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F27" s="32">
         <v>4996</v>
@@ -16762,7 +16773,7 @@
         <v>40140</v>
       </c>
       <c r="J27" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K27" s="36">
         <v>100449</v>
@@ -16771,7 +16782,7 @@
         <v>46036</v>
       </c>
       <c r="M27" s="28" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="N27" s="36">
         <v>4359940</v>
@@ -16789,7 +16800,7 @@
         <v>14</v>
       </c>
       <c r="S27" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -16800,13 +16811,13 @@
         <v>8</v>
       </c>
       <c r="C28" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D28" s="30" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E28" s="31" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F28" s="32">
         <v>3560</v>
@@ -16818,10 +16829,10 @@
         <v>242</v>
       </c>
       <c r="I28" s="52" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="J28" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K28" s="36">
         <v>99421</v>
@@ -16830,7 +16841,7 @@
         <v>46032</v>
       </c>
       <c r="M28" s="28" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="N28" s="36">
         <v>4355691</v>
@@ -16848,7 +16859,7 @@
         <v>10</v>
       </c>
       <c r="S28" s="46" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -16859,13 +16870,13 @@
         <v>8</v>
       </c>
       <c r="C29" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D29" s="30" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E29" s="31" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F29" s="32">
         <v>25810.69</v>
@@ -16880,7 +16891,7 @@
         <v>43493</v>
       </c>
       <c r="J29" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K29" s="36">
         <v>99314</v>
@@ -16889,7 +16900,7 @@
         <v>46032</v>
       </c>
       <c r="M29" s="28" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="N29" s="36">
         <v>4355697</v>
@@ -16907,7 +16918,7 @@
         <v>10</v>
       </c>
       <c r="S29" s="46" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -16918,13 +16929,13 @@
         <v>8</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D30" s="30" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E30" s="31" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F30" s="32">
         <v>25031.200000000001</v>
@@ -16939,7 +16950,7 @@
         <v>43493</v>
       </c>
       <c r="J30" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K30" s="36">
         <v>99383</v>
@@ -16948,7 +16959,7 @@
         <v>46032</v>
       </c>
       <c r="M30" s="28" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="N30" s="36">
         <v>4355700</v>
@@ -16966,7 +16977,7 @@
         <v>10</v>
       </c>
       <c r="S30" s="46" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="31" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -16977,13 +16988,13 @@
         <v>8</v>
       </c>
       <c r="C31" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D31" s="30" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E31" s="31" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F31" s="32">
         <v>43549.7</v>
@@ -16998,7 +17009,7 @@
         <v>41757</v>
       </c>
       <c r="J31" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K31" s="36">
         <v>99709</v>
@@ -17007,7 +17018,7 @@
         <v>46032</v>
       </c>
       <c r="M31" s="28" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="N31" s="36">
         <v>4355702</v>
@@ -17025,7 +17036,7 @@
         <v>14</v>
       </c>
       <c r="S31" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -17036,13 +17047,13 @@
         <v>8</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D32" s="30" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E32" s="31" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F32" s="32">
         <v>6150</v>
@@ -17057,7 +17068,7 @@
         <v>42639</v>
       </c>
       <c r="J32" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K32" s="36">
         <v>99712</v>
@@ -17066,7 +17077,7 @@
         <v>46032</v>
       </c>
       <c r="M32" s="28" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="N32" s="36">
         <v>4355763</v>
@@ -17084,7 +17095,7 @@
         <v>14</v>
       </c>
       <c r="S32" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -17095,13 +17106,13 @@
         <v>8</v>
       </c>
       <c r="C33" s="29" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D33" s="30" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E33" s="31" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F33" s="32">
         <v>3200</v>
@@ -17116,7 +17127,7 @@
         <v>42766</v>
       </c>
       <c r="J33" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K33" s="36">
         <v>99864</v>
@@ -17125,7 +17136,7 @@
         <v>46031</v>
       </c>
       <c r="M33" s="28" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="N33" s="36">
         <v>4355439</v>
@@ -17143,7 +17154,7 @@
         <v>10</v>
       </c>
       <c r="S33" s="46" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="34" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -17154,13 +17165,13 @@
         <v>8</v>
       </c>
       <c r="C34" s="29" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D34" s="30" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E34" s="31" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F34" s="32">
         <v>1900</v>
@@ -17175,7 +17186,7 @@
         <v>42767</v>
       </c>
       <c r="J34" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K34" s="36">
         <v>99861</v>
@@ -17184,7 +17195,7 @@
         <v>46031</v>
       </c>
       <c r="M34" s="28" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="N34" s="36">
         <v>4355433</v>
@@ -17202,7 +17213,7 @@
         <v>10</v>
       </c>
       <c r="S34" s="46" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="35" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -17213,13 +17224,13 @@
         <v>8</v>
       </c>
       <c r="C35" s="29" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D35" s="30" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E35" s="31" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F35" s="32">
         <v>2420</v>
@@ -17234,7 +17245,7 @@
         <v>43168</v>
       </c>
       <c r="J35" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K35" s="36">
         <v>99296</v>
@@ -17243,7 +17254,7 @@
         <v>46030</v>
       </c>
       <c r="M35" s="28" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="N35" s="36">
         <v>4353367</v>
@@ -17261,7 +17272,7 @@
         <v>10</v>
       </c>
       <c r="S35" s="46" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="36" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -17272,13 +17283,13 @@
         <v>8</v>
       </c>
       <c r="C36" s="29" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D36" s="30" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E36" s="31" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F36" s="32">
         <v>12500</v>
@@ -17290,10 +17301,10 @@
         <v>242</v>
       </c>
       <c r="I36" s="39" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J36" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K36" s="36">
         <v>99291</v>
@@ -17302,7 +17313,7 @@
         <v>46030</v>
       </c>
       <c r="M36" s="28" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="N36" s="36">
         <v>4353384</v>
@@ -17320,7 +17331,7 @@
         <v>14</v>
       </c>
       <c r="S36" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -17331,13 +17342,13 @@
         <v>8</v>
       </c>
       <c r="C37" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D37" s="30" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E37" s="31" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F37" s="32">
         <v>5300</v>
@@ -17352,7 +17363,7 @@
         <v>41750</v>
       </c>
       <c r="J37" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K37" s="36">
         <v>99479</v>
@@ -17361,7 +17372,7 @@
         <v>46030</v>
       </c>
       <c r="M37" s="28" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="N37" s="36">
         <v>4353433</v>
@@ -17379,7 +17390,7 @@
         <v>10</v>
       </c>
       <c r="S37" s="46" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="38" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -17390,13 +17401,13 @@
         <v>8</v>
       </c>
       <c r="C38" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D38" s="30" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E38" s="31" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F38" s="32">
         <v>3898.2</v>
@@ -17411,7 +17422,7 @@
         <v>42805</v>
       </c>
       <c r="J38" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K38" s="36">
         <v>99619</v>
@@ -17420,7 +17431,7 @@
         <v>46030</v>
       </c>
       <c r="M38" s="28" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="N38" s="36">
         <v>4353480</v>
@@ -17438,7 +17449,7 @@
         <v>10</v>
       </c>
       <c r="S38" s="46" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="39" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -17449,13 +17460,13 @@
         <v>8</v>
       </c>
       <c r="C39" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D39" s="30" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E39" s="31" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F39" s="32">
         <v>2209.37</v>
@@ -17467,10 +17478,10 @@
         <v>242</v>
       </c>
       <c r="I39" s="34" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J39" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K39" s="36">
         <v>98699</v>
@@ -17479,7 +17490,7 @@
         <v>46030</v>
       </c>
       <c r="M39" s="28" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="N39" s="36">
         <v>4354005</v>
@@ -17497,7 +17508,7 @@
         <v>14</v>
       </c>
       <c r="S39" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -17508,13 +17519,13 @@
         <v>8</v>
       </c>
       <c r="C40" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D40" s="30" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E40" s="31" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F40" s="32">
         <v>45045.8</v>
@@ -17526,10 +17537,10 @@
         <v>242</v>
       </c>
       <c r="I40" s="34" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="J40" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K40" s="36">
         <v>99170</v>
@@ -17538,7 +17549,7 @@
         <v>46029</v>
       </c>
       <c r="M40" s="28" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="N40" s="36">
         <v>4352661</v>
@@ -17556,7 +17567,7 @@
         <v>14</v>
       </c>
       <c r="S40" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="41" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -17567,13 +17578,13 @@
         <v>8</v>
       </c>
       <c r="C41" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D41" s="30" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E41" s="31" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="F41" s="32">
         <v>5900</v>
@@ -17588,7 +17599,7 @@
         <v>42617</v>
       </c>
       <c r="J41" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K41" s="36">
         <v>98534</v>
@@ -17597,7 +17608,7 @@
         <v>46027</v>
       </c>
       <c r="M41" s="28" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="N41" s="36">
         <v>4348310</v>
@@ -17615,7 +17626,7 @@
         <v>10</v>
       </c>
       <c r="S41" s="46" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="42" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -17626,13 +17637,13 @@
         <v>8</v>
       </c>
       <c r="C42" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D42" s="30" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E42" s="31" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="F42" s="32">
         <v>8259.89</v>
@@ -17647,7 +17658,7 @@
         <v>40284</v>
       </c>
       <c r="J42" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K42" s="36">
         <v>97676</v>
@@ -17656,7 +17667,7 @@
         <v>46014</v>
       </c>
       <c r="M42" s="28" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="N42" s="36">
         <v>4340049</v>
@@ -17674,7 +17685,7 @@
         <v>10</v>
       </c>
       <c r="S42" s="46" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -17685,13 +17696,13 @@
         <v>8</v>
       </c>
       <c r="C43" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D43" s="30" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E43" s="31" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F43" s="32">
         <v>40053.78</v>
@@ -17706,7 +17717,7 @@
         <v>41757</v>
       </c>
       <c r="J43" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K43" s="36">
         <v>97208</v>
@@ -17715,7 +17726,7 @@
         <v>46013</v>
       </c>
       <c r="M43" s="28" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="N43" s="36">
         <v>4338670</v>
@@ -17733,7 +17744,7 @@
         <v>14</v>
       </c>
       <c r="S43" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -17744,13 +17755,13 @@
         <v>8</v>
       </c>
       <c r="C44" s="29" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D44" s="30" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E44" s="31" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F44" s="32">
         <v>3999</v>
@@ -17765,7 +17776,7 @@
         <v>42561</v>
       </c>
       <c r="J44" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K44" s="36">
         <v>97358</v>
@@ -17774,7 +17785,7 @@
         <v>46010</v>
       </c>
       <c r="M44" s="28" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="N44" s="36">
         <v>4336121</v>
@@ -17792,7 +17803,7 @@
         <v>10</v>
       </c>
       <c r="S44" s="46" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="45" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -17803,13 +17814,13 @@
         <v>8</v>
       </c>
       <c r="C45" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D45" s="30" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E45" s="31" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F45" s="32">
         <v>7153.5</v>
@@ -17824,7 +17835,7 @@
         <v>42410</v>
       </c>
       <c r="J45" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K45" s="36">
         <v>96888</v>
@@ -17833,7 +17844,7 @@
         <v>46007</v>
       </c>
       <c r="M45" s="28" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="N45" s="36">
         <v>4332711</v>
@@ -17851,7 +17862,7 @@
         <v>10</v>
       </c>
       <c r="S45" s="46" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="46" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -17862,13 +17873,13 @@
         <v>8</v>
       </c>
       <c r="C46" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D46" s="30" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E46" s="31" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F46" s="32">
         <v>1080</v>
@@ -17880,10 +17891,10 @@
         <v>242</v>
       </c>
       <c r="I46" s="34" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J46" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K46" s="36">
         <v>96451</v>
@@ -17892,7 +17903,7 @@
         <v>46006</v>
       </c>
       <c r="M46" s="28" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="N46" s="36">
         <v>4330779</v>
@@ -17910,7 +17921,7 @@
         <v>10</v>
       </c>
       <c r="S46" s="46" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="47" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -17921,13 +17932,13 @@
         <v>8</v>
       </c>
       <c r="C47" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D47" s="30" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E47" s="31" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F47" s="32">
         <v>40865.75</v>
@@ -17939,10 +17950,10 @@
         <v>242</v>
       </c>
       <c r="I47" s="34" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J47" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K47" s="36">
         <v>95447</v>
@@ -17951,7 +17962,7 @@
         <v>46006</v>
       </c>
       <c r="M47" s="28" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="N47" s="36">
         <v>4330454</v>
@@ -17969,7 +17980,7 @@
         <v>10</v>
       </c>
       <c r="S47" s="46" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="48" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -17980,13 +17991,13 @@
         <v>8</v>
       </c>
       <c r="C48" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D48" s="30" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E48" s="31" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F48" s="32">
         <v>35530.239999999998</v>
@@ -18001,7 +18012,7 @@
         <v>39060</v>
       </c>
       <c r="J48" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K48" s="36">
         <v>92761</v>
@@ -18010,7 +18021,7 @@
         <v>45994</v>
       </c>
       <c r="M48" s="28" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="N48" s="36">
         <v>4320200</v>
@@ -18028,7 +18039,7 @@
         <v>14</v>
       </c>
       <c r="S48" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="49" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -18039,13 +18050,13 @@
         <v>8</v>
       </c>
       <c r="C49" s="29" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D49" s="30" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E49" s="31" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F49" s="32">
         <v>7600</v>
@@ -18057,10 +18068,10 @@
         <v>5</v>
       </c>
       <c r="I49" s="34" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J49" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K49" s="36">
         <v>94653</v>
@@ -18069,7 +18080,7 @@
         <v>45993</v>
       </c>
       <c r="M49" s="28" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="N49" s="36">
         <v>4318988</v>
@@ -18087,7 +18098,7 @@
         <v>10</v>
       </c>
       <c r="S49" s="46" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="50" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -18098,13 +18109,13 @@
         <v>8</v>
       </c>
       <c r="C50" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D50" s="30" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E50" s="31" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F50" s="40">
         <v>53200</v>
@@ -18119,7 +18130,7 @@
         <v>32847</v>
       </c>
       <c r="J50" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K50" s="36">
         <v>87399</v>
@@ -18128,7 +18139,7 @@
         <v>45986</v>
       </c>
       <c r="M50" s="28" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="N50" s="36">
         <v>4310675</v>
@@ -18146,7 +18157,7 @@
         <v>14</v>
       </c>
       <c r="S50" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="51" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -18157,13 +18168,13 @@
         <v>8</v>
       </c>
       <c r="C51" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D51" s="30" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E51" s="31" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="F51" s="32">
         <v>9690.33</v>
@@ -18178,7 +18189,7 @@
         <v>37478</v>
       </c>
       <c r="J51" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K51" s="36">
         <v>87407</v>
@@ -18187,7 +18198,7 @@
         <v>45981</v>
       </c>
       <c r="M51" s="28" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="N51" s="36">
         <v>4306425</v>
@@ -18205,7 +18216,7 @@
         <v>14</v>
       </c>
       <c r="S51" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="52" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -18216,13 +18227,13 @@
         <v>8</v>
       </c>
       <c r="C52" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D52" s="30" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E52" s="31" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F52" s="32">
         <v>1755</v>
@@ -18234,10 +18245,10 @@
         <v>242</v>
       </c>
       <c r="I52" s="34" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J52" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K52" s="36">
         <v>88232</v>
@@ -18246,7 +18257,7 @@
         <v>45957</v>
       </c>
       <c r="M52" s="28" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="N52" s="36">
         <v>4281851</v>
@@ -18264,7 +18275,7 @@
         <v>10</v>
       </c>
       <c r="S52" s="46" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="53" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -18275,13 +18286,13 @@
         <v>8</v>
       </c>
       <c r="C53" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D53" s="30" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E53" s="31" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F53" s="32">
         <v>38046.94</v>
@@ -18296,7 +18307,7 @@
         <v>37258</v>
       </c>
       <c r="J53" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K53" s="36">
         <v>85500</v>
@@ -18305,7 +18316,7 @@
         <v>45939</v>
       </c>
       <c r="M53" s="28" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="N53" s="36">
         <v>4266419</v>
@@ -18323,7 +18334,7 @@
         <v>10</v>
       </c>
       <c r="S53" s="46" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="54" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -18334,13 +18345,13 @@
         <v>8</v>
       </c>
       <c r="C54" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D54" s="30" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E54" s="31" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F54" s="32">
         <v>52933.41</v>
@@ -18355,7 +18366,7 @@
         <v>37477</v>
       </c>
       <c r="J54" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K54" s="36">
         <v>85866</v>
@@ -18364,7 +18375,7 @@
         <v>45939</v>
       </c>
       <c r="M54" s="28" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="N54" s="36">
         <v>4266452</v>
@@ -18382,7 +18393,7 @@
         <v>14</v>
       </c>
       <c r="S54" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="55" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -18393,13 +18404,13 @@
         <v>8</v>
       </c>
       <c r="C55" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D55" s="30" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E55" s="31" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F55" s="32">
         <v>63723.28</v>
@@ -18411,10 +18422,10 @@
         <v>242</v>
       </c>
       <c r="I55" s="34" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J55" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K55" s="36">
         <v>79952</v>
@@ -18423,7 +18434,7 @@
         <v>45919</v>
       </c>
       <c r="M55" s="28" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="N55" s="36">
         <v>4247386</v>
@@ -18441,7 +18452,7 @@
         <v>10</v>
       </c>
       <c r="S55" s="46" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="56" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -18452,13 +18463,13 @@
         <v>8</v>
       </c>
       <c r="C56" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D56" s="30" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E56" s="31" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F56" s="32">
         <v>16488.73</v>
@@ -18470,10 +18481,10 @@
         <v>242</v>
       </c>
       <c r="I56" s="34" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J56" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K56" s="36">
         <v>79957</v>
@@ -18482,7 +18493,7 @@
         <v>45909</v>
       </c>
       <c r="M56" s="28" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="N56" s="36">
         <v>4235917</v>
@@ -18500,7 +18511,7 @@
         <v>14</v>
       </c>
       <c r="S56" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="57" spans="1:19" ht="83.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -18511,13 +18522,13 @@
         <v>8</v>
       </c>
       <c r="C57" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D57" s="30" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E57" s="31" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F57" s="32">
         <v>61000</v>
@@ -18529,10 +18540,10 @@
         <v>5</v>
       </c>
       <c r="I57" s="34" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J57" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K57" s="36">
         <v>72312</v>
@@ -18541,7 +18552,7 @@
         <v>45856</v>
       </c>
       <c r="M57" s="28" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="N57" s="36">
         <v>4183033</v>
@@ -18559,7 +18570,7 @@
         <v>14</v>
       </c>
       <c r="S57" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="58" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -18570,13 +18581,13 @@
         <v>8</v>
       </c>
       <c r="C58" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D58" s="30" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E58" s="31" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F58" s="32">
         <v>49000</v>
@@ -18588,10 +18599,10 @@
         <v>242</v>
       </c>
       <c r="I58" s="34" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J58" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K58" s="36">
         <v>68049</v>
@@ -18600,7 +18611,7 @@
         <v>45827</v>
       </c>
       <c r="M58" s="28" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="N58" s="36">
         <v>4152135</v>
@@ -18618,7 +18629,7 @@
         <v>14</v>
       </c>
       <c r="S58" s="49" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="59" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -18629,13 +18640,13 @@
         <v>8</v>
       </c>
       <c r="C59" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D59" s="30" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E59" s="31" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F59" s="32">
         <v>3955</v>
@@ -18650,7 +18661,7 @@
         <v>45067</v>
       </c>
       <c r="J59" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K59" s="36">
         <v>103899</v>
@@ -18659,7 +18670,7 @@
         <v>46058</v>
       </c>
       <c r="M59" s="28" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="N59" s="36">
         <v>4383130</v>
@@ -18677,7 +18688,7 @@
         <v>10</v>
       </c>
       <c r="S59" s="46" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="60" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -18688,13 +18699,13 @@
         <v>8</v>
       </c>
       <c r="C60" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D60" s="30" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E60" s="31" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F60" s="32">
         <v>7678.4</v>
@@ -18709,7 +18720,7 @@
         <v>41742</v>
       </c>
       <c r="J60" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K60" s="36">
         <v>100101</v>
@@ -18718,7 +18729,7 @@
         <v>46039</v>
       </c>
       <c r="M60" s="28" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="N60" s="36">
         <v>4382543</v>
@@ -18734,7 +18745,7 @@
         <v>14</v>
       </c>
       <c r="S60" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="61" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -18745,16 +18756,16 @@
         <v>8</v>
       </c>
       <c r="C61" s="29" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D61" s="30" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E61" s="31" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F61" s="32" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="G61" s="33" t="s">
         <v>20</v>
@@ -18763,10 +18774,10 @@
         <v>5</v>
       </c>
       <c r="I61" s="34" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J61" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K61" s="36">
         <v>97379</v>
@@ -18785,7 +18796,7 @@
         <v>14</v>
       </c>
       <c r="S61" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="62" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -18796,13 +18807,13 @@
         <v>8</v>
       </c>
       <c r="C62" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D62" s="30" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E62" s="31" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="F62" s="40">
         <v>4800</v>
@@ -18817,7 +18828,7 @@
         <v>44127</v>
       </c>
       <c r="J62" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K62" s="36">
         <v>104381</v>
@@ -18826,7 +18837,7 @@
         <v>46058</v>
       </c>
       <c r="M62" s="28" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="N62" s="30">
         <v>4382996</v>
@@ -18842,7 +18853,7 @@
         <v>14</v>
       </c>
       <c r="S62" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="63" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -18853,13 +18864,13 @@
         <v>8</v>
       </c>
       <c r="C63" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D63" s="30" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E63" s="31" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F63" s="40">
         <v>10080</v>
@@ -18874,7 +18885,7 @@
         <v>44127</v>
       </c>
       <c r="J63" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K63" s="36">
         <v>104383</v>
@@ -18883,7 +18894,7 @@
         <v>46058</v>
       </c>
       <c r="M63" s="28" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="N63" s="30">
         <v>4383189</v>
@@ -18901,7 +18912,7 @@
         <v>10</v>
       </c>
       <c r="S63" s="46" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="64" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -18912,13 +18923,13 @@
         <v>8</v>
       </c>
       <c r="C64" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D64" s="30" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E64" s="31" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F64" s="40">
         <v>17450</v>
@@ -18930,10 +18941,10 @@
         <v>242</v>
       </c>
       <c r="I64" s="34" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J64" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K64" s="36">
         <v>103904</v>
@@ -18942,7 +18953,7 @@
         <v>46058</v>
       </c>
       <c r="M64" s="28" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="N64" s="30">
         <v>4383166</v>
@@ -18960,7 +18971,7 @@
         <v>10</v>
       </c>
       <c r="S64" s="46" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="65" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -18971,13 +18982,13 @@
         <v>8</v>
       </c>
       <c r="C65" s="28" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D65" s="30" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E65" s="43" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F65" s="44">
         <v>1120</v>
@@ -18992,7 +19003,7 @@
         <v>37018</v>
       </c>
       <c r="J65" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K65" s="28">
         <v>104443</v>
@@ -19001,7 +19012,7 @@
         <v>46058</v>
       </c>
       <c r="M65" s="28" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="N65" s="28">
         <v>4383152</v>
@@ -19017,7 +19028,7 @@
         <v>14</v>
       </c>
       <c r="S65" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="66" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -19028,13 +19039,13 @@
         <v>8</v>
       </c>
       <c r="C66" s="28" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D66" s="30" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E66" s="43" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F66" s="44">
         <v>5840</v>
@@ -19049,14 +19060,14 @@
         <v>43711</v>
       </c>
       <c r="J66" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K66" s="28">
         <v>104445</v>
       </c>
       <c r="L66" s="28"/>
       <c r="M66" s="28" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="N66" s="28"/>
       <c r="O66" s="28"/>
@@ -19070,7 +19081,7 @@
         <v>14</v>
       </c>
       <c r="S66" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="67" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -19081,13 +19092,13 @@
         <v>8</v>
       </c>
       <c r="C67" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D67" s="42" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E67" s="43" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="F67" s="44">
         <v>4898.2</v>
@@ -19102,14 +19113,14 @@
         <v>44138</v>
       </c>
       <c r="J67" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K67" s="28">
         <v>104937</v>
       </c>
       <c r="L67" s="28"/>
       <c r="M67" s="28" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="N67" s="28"/>
       <c r="O67" s="28"/>
@@ -19123,7 +19134,7 @@
         <v>14</v>
       </c>
       <c r="S67" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="68" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -19134,13 +19145,13 @@
         <v>8</v>
       </c>
       <c r="C68" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D68" s="42" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E68" s="43" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="F68" s="44">
         <v>7694.5</v>
@@ -19155,7 +19166,7 @@
         <v>42965</v>
       </c>
       <c r="J68" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K68" s="28">
         <v>104943</v>
@@ -19164,7 +19175,7 @@
         <v>46064</v>
       </c>
       <c r="M68" s="28" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="N68" s="28">
         <v>4388677</v>
@@ -19180,7 +19191,7 @@
         <v>14</v>
       </c>
       <c r="S68" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="69" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -19191,13 +19202,13 @@
         <v>8</v>
       </c>
       <c r="C69" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D69" s="42" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E69" s="43" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F69" s="44">
         <v>17776</v>
@@ -19212,7 +19223,7 @@
         <v>42965</v>
       </c>
       <c r="J69" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K69" s="28">
         <v>104944</v>
@@ -19221,7 +19232,7 @@
         <v>46064</v>
       </c>
       <c r="M69" s="28" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="N69" s="28">
         <v>4388710</v>
@@ -19237,7 +19248,7 @@
         <v>14</v>
       </c>
       <c r="S69" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="70" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -19248,13 +19259,13 @@
         <v>8</v>
       </c>
       <c r="C70" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D70" s="42" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E70" s="43" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F70" s="44">
         <v>11757</v>
@@ -19269,7 +19280,7 @@
         <v>44708</v>
       </c>
       <c r="J70" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K70" s="28">
         <v>105178</v>
@@ -19278,7 +19289,7 @@
         <v>46064</v>
       </c>
       <c r="M70" s="28" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="N70" s="28">
         <v>105178</v>
@@ -19294,7 +19305,7 @@
         <v>14</v>
       </c>
       <c r="S70" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="71" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -19305,13 +19316,13 @@
         <v>8</v>
       </c>
       <c r="C71" s="28" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D71" s="30" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E71" s="43" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="F71" s="44">
         <v>950</v>
@@ -19326,14 +19337,14 @@
         <v>45311</v>
       </c>
       <c r="J71" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K71" s="28">
         <v>105856</v>
       </c>
       <c r="L71" s="28"/>
       <c r="M71" s="28" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="N71" s="28"/>
       <c r="O71" s="28"/>
@@ -19347,7 +19358,7 @@
         <v>14</v>
       </c>
       <c r="S71" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="72" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -19358,13 +19369,13 @@
         <v>8</v>
       </c>
       <c r="C72" s="28" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D72" s="30" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E72" s="43" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F72" s="44">
         <v>6150</v>
@@ -19379,14 +19390,14 @@
         <v>45047</v>
       </c>
       <c r="J72" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K72" s="28">
         <v>105857</v>
       </c>
       <c r="L72" s="28"/>
       <c r="M72" s="28" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="N72" s="28"/>
       <c r="O72" s="28"/>
@@ -19400,7 +19411,7 @@
         <v>14</v>
       </c>
       <c r="S72" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="73" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -19411,13 +19422,13 @@
         <v>8</v>
       </c>
       <c r="C73" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D73" s="42" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E73" s="43" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F73" s="44">
         <v>7700</v>
@@ -19432,14 +19443,14 @@
         <v>44334</v>
       </c>
       <c r="J73" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K73" s="28">
         <v>106477</v>
       </c>
       <c r="L73" s="28"/>
       <c r="M73" s="28" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="N73" s="28"/>
       <c r="O73" s="28"/>
@@ -19453,7 +19464,7 @@
         <v>14</v>
       </c>
       <c r="S73" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="74" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -19464,13 +19475,13 @@
         <v>8</v>
       </c>
       <c r="C74" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D74" s="42" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E74" s="43" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="F74" s="44">
         <v>3300</v>
@@ -19485,7 +19496,7 @@
         <v>44748</v>
       </c>
       <c r="J74" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K74" s="28">
         <v>106483</v>
@@ -19494,7 +19505,7 @@
         <v>46070</v>
       </c>
       <c r="M74" s="28" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="N74" s="28">
         <v>4394789</v>
@@ -19510,7 +19521,7 @@
         <v>14</v>
       </c>
       <c r="S74" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="75" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -19521,13 +19532,13 @@
         <v>8</v>
       </c>
       <c r="C75" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D75" s="42" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E75" s="43" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F75" s="44">
         <v>6120</v>
@@ -19539,17 +19550,17 @@
         <v>242</v>
       </c>
       <c r="I75" s="41" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="J75" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K75" s="28">
         <v>106485</v>
       </c>
       <c r="L75" s="28"/>
       <c r="M75" s="28" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="N75" s="28"/>
       <c r="O75" s="28"/>
@@ -19563,7 +19574,7 @@
         <v>14</v>
       </c>
       <c r="S75" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="76" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -19574,13 +19585,13 @@
         <v>8</v>
       </c>
       <c r="C76" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D76" s="30" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E76" s="43" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F76" s="44">
         <v>32400</v>
@@ -19592,17 +19603,17 @@
         <v>242</v>
       </c>
       <c r="I76" s="34" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J76" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K76" s="28">
         <v>106661</v>
       </c>
       <c r="L76" s="28"/>
       <c r="M76" s="28" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="N76" s="28"/>
       <c r="O76" s="28"/>
@@ -19616,7 +19627,7 @@
         <v>14</v>
       </c>
       <c r="S76" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="77" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -19627,13 +19638,13 @@
         <v>8</v>
       </c>
       <c r="C77" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D77" s="30" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E77" s="43" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="F77" s="44">
         <v>3507</v>
@@ -19648,14 +19659,14 @@
         <v>45638</v>
       </c>
       <c r="J77" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K77" s="28">
         <v>106753</v>
       </c>
       <c r="L77" s="28"/>
       <c r="M77" s="28" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="N77" s="28"/>
       <c r="O77" s="28"/>
@@ -19669,7 +19680,7 @@
         <v>14</v>
       </c>
       <c r="S77" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="78" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -19680,13 +19691,13 @@
         <v>8</v>
       </c>
       <c r="C78" s="29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D78" s="30" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E78" s="43" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="F78" s="44">
         <v>586</v>
@@ -19701,14 +19712,14 @@
         <v>45508</v>
       </c>
       <c r="J78" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K78" s="28">
         <v>106755</v>
       </c>
       <c r="L78" s="28"/>
       <c r="M78" s="28" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="N78" s="28"/>
       <c r="O78" s="28"/>
@@ -19722,7 +19733,7 @@
         <v>14</v>
       </c>
       <c r="S78" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="79" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -19733,13 +19744,13 @@
         <v>8</v>
       </c>
       <c r="C79" s="28" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D79" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="E79" s="53" t="s">
-        <v>237</v>
+        <v>159</v>
+      </c>
+      <c r="E79" s="43" t="s">
+        <v>239</v>
       </c>
       <c r="F79" s="44">
         <v>7513.05</v>
@@ -19754,14 +19765,14 @@
         <v>44818</v>
       </c>
       <c r="J79" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K79" s="28">
         <v>106784</v>
       </c>
       <c r="L79" s="28"/>
       <c r="M79" s="28" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="N79" s="28"/>
       <c r="O79" s="28"/>
@@ -19775,31 +19786,53 @@
         <v>14</v>
       </c>
       <c r="S79" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="80" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="27">
         <v>79</v>
       </c>
-      <c r="B80" s="28"/>
-      <c r="C80" s="28"/>
-      <c r="D80" s="42"/>
-      <c r="E80" s="43"/>
-      <c r="F80" s="44"/>
-      <c r="G80" s="28"/>
-      <c r="H80" s="28"/>
-      <c r="I80" s="41"/>
-      <c r="J80" s="41"/>
+      <c r="B80" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="C80" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="D80" s="30" t="s">
+        <v>240</v>
+      </c>
+      <c r="E80" s="43" t="s">
+        <v>241</v>
+      </c>
+      <c r="F80" s="44">
+        <v>1000</v>
+      </c>
+      <c r="G80" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="H80" s="28">
+        <v>242</v>
+      </c>
+      <c r="I80" s="34"/>
+      <c r="J80" s="35"/>
       <c r="K80" s="28"/>
       <c r="L80" s="28"/>
       <c r="M80" s="28"/>
       <c r="N80" s="28"/>
       <c r="O80" s="28"/>
-      <c r="P80" s="28"/>
-      <c r="Q80" s="28"/>
-      <c r="R80" s="28"/>
-      <c r="S80" s="41"/>
+      <c r="P80" s="47" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q80" s="47" t="s">
+        <v>10</v>
+      </c>
+      <c r="R80" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="S80" s="48" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="81" spans="1:19" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="27">
@@ -29542,13 +29575,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6dbcbc56-3d12-411a-a735-f36ec8e8bfd2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -29781,20 +29813,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6dbcbc56-3d12-411a-a735-f36ec8e8bfd2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60843E7F-DCA1-4FBE-8AEE-F739F63FAD5F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDDA4EE2-72BB-4CD5-80FF-EAFC698EEABA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6dbcbc56-3d12-411a-a735-f36ec8e8bfd2"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -29819,9 +29850,11 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDDA4EE2-72BB-4CD5-80FF-EAFC698EEABA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60843E7F-DCA1-4FBE-8AEE-F739F63FAD5F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6dbcbc56-3d12-411a-a735-f36ec8e8bfd2"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>